--- a/artfynd/A 60140-2025 artfynd.xlsx
+++ b/artfynd/A 60140-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>277508</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600024.5429468524</v>
+        <v>600025</v>
       </c>
       <c r="R2" t="n">
-        <v>6283547.149367108</v>
+        <v>6283547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2000-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,19 +768,18 @@
           <t>Via Helena Lager</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>67610256</v>
       </c>
       <c r="B3" t="n">
-        <v>97512</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600076.563796127</v>
+        <v>600077</v>
       </c>
       <c r="R3" t="n">
-        <v>6283512.676993038</v>
+        <v>6283513</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,19 +847,9 @@
           <t>2017-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,22 +869,21 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Waldenström, Liselotte Wetterstrand Waldenström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Liselotte Wetterstrand Waldenström, Anders Waldenström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67610239</v>
+        <v>67610264</v>
       </c>
       <c r="B4" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,21 +891,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>174</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600076.563796127</v>
+        <v>600114</v>
       </c>
       <c r="R4" t="n">
-        <v>6283512.676993038</v>
+        <v>6283554</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,19 +951,9 @@
           <t>2017-07-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +973,222 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Liselotte Wetterstrand Waldenström, Anders Waldenström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>67610305</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100346</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>174</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Strävlosta</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bromopsis benekenii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Lange) Holub</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vanserum V, Öl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>600182</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6283504</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Runsten</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-07-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-07-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Waldenström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Anders Waldenström, Liselotte Wetterstrand Waldenström</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>67610239</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vanserum V, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>600077</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6283513</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Runsten</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-07-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-07-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Waldenström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Waldenström, Liselotte Wetterstrand Waldenström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60140-2025 artfynd.xlsx
+++ b/artfynd/A 60140-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/277508</t>
         </is>
       </c>
     </row>
@@ -877,6 +887,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67610256</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67610264</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67610305</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,8 +1214,20 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67610239</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>